--- a/docs/StructureDefinition-HAHMedicationRequest.xlsx
+++ b/docs/StructureDefinition-HAHMedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4692" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4690" uniqueCount="776">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T17:33:17+08:00</t>
+    <t>2026-09-29T04:34:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2332,7 +2332,7 @@
     <t>這個資料項目被標記為修飾用，因為無論是否允許替換，它都不能被忽略。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode|3.0.0</t>
   </si>
   <si>
     <t>code</t>
@@ -2350,7 +2350,7 @@
     <t>表示替換的原因，或為什麼必須或不必須進行替換。</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason|3.0.0</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -2743,15 +2743,15 @@
   <dimension ref="A1:AO126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="79.11328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.40234375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="77.38671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.81640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2762,27 +2762,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.5703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.51171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="49.234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="237.45703125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="113.05078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16997,9 +16997,7 @@
       <c r="X122" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y122" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
         <v>746</v>
       </c>
@@ -17112,9 +17110,7 @@
       <c r="X123" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y123" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
         <v>752</v>
       </c>
